--- a/Team-Data/2014-15/2-7-2014-15.xlsx
+++ b/Team-Data/2014-15/2-7-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -772,13 +839,13 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
         <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
@@ -802,7 +869,7 @@
         <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -864,16 +931,16 @@
         <v>87.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L3" t="n">
         <v>7.6</v>
       </c>
       <c r="M3" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
         <v>14.9</v>
@@ -882,7 +949,7 @@
         <v>19.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
@@ -894,7 +961,7 @@
         <v>43.5</v>
       </c>
       <c r="U3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="V3" t="n">
         <v>14.4</v>
@@ -903,25 +970,25 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
         <v>5.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AB3" t="n">
-        <v>101</v>
+        <v>101.2</v>
       </c>
       <c r="AC3" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>21</v>
@@ -933,7 +1000,7 @@
         <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
         <v>4</v>
@@ -951,49 +1018,49 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.42</v>
+        <v>0.429</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J4" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O4" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P4" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
         <v>14.3</v>
@@ -1097,13 +1164,13 @@
         <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.9</v>
+        <v>-3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1121,7 +1188,7 @@
         <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>18</v>
@@ -1139,7 +1206,7 @@
         <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>20</v>
@@ -1148,13 +1215,13 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
         <v>14</v>
@@ -1166,19 +1233,19 @@
         <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -1207,49 +1274,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
         <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.44</v>
+        <v>0.449</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J5" t="n">
         <v>84.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="O5" t="n">
         <v>17.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.734</v>
+        <v>0.732</v>
       </c>
       <c r="R5" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S5" t="n">
         <v>33.9</v>
@@ -1264,7 +1331,7 @@
         <v>11.8</v>
       </c>
       <c r="W5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
@@ -1279,13 +1346,13 @@
         <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.5</v>
+        <v>94.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1297,10 +1364,10 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
         <v>10</v>
@@ -1318,25 +1385,25 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS5" t="n">
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.608</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M6" t="n">
         <v>21.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O6" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="P6" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S6" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T6" t="n">
         <v>46</v>
       </c>
       <c r="U6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V6" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W6" t="n">
         <v>6.2</v>
@@ -1455,22 +1522,22 @@
         <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1479,16 +1546,16 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="n">
         <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
@@ -1506,13 +1573,13 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="n">
         <v>3</v>
       </c>
-      <c r="AR6" t="n">
-        <v>2</v>
-      </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
@@ -1521,7 +1588,7 @@
         <v>18</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1530,10 +1597,10 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1664,10 +1731,10 @@
         <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>14</v>
@@ -1685,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
@@ -1694,16 +1761,16 @@
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
       </c>
       <c r="AU7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1715,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -1756,64 +1823,64 @@
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.673</v>
+        <v>0.654</v>
       </c>
       <c r="H8" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J8" t="n">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="L8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.359</v>
       </c>
       <c r="O8" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.5</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
         <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="n">
         <v>3.6</v>
@@ -1822,61 +1889,61 @@
         <v>19.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>107</v>
+        <v>106.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
         <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS8" t="n">
         <v>21</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>20</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
         <v>22</v>
@@ -2028,16 +2095,16 @@
         <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
         <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM9" t="n">
         <v>12</v>
@@ -2055,7 +2122,7 @@
         <v>22</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2067,7 +2134,7 @@
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2085,10 +2152,10 @@
         <v>12</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>22</v>
@@ -2246,10 +2313,10 @@
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
         <v>12</v>
@@ -2264,7 +2331,7 @@
         <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="J11" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.483</v>
@@ -2326,10 +2393,10 @@
         <v>10.5</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.39</v>
+        <v>0.388</v>
       </c>
       <c r="O11" t="n">
         <v>16.8</v>
@@ -2338,7 +2405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R11" t="n">
         <v>10.5</v>
@@ -2350,7 +2417,7 @@
         <v>45.1</v>
       </c>
       <c r="U11" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="V11" t="n">
         <v>14.9</v>
@@ -2368,16 +2435,16 @@
         <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB11" t="n">
-        <v>111.3</v>
+        <v>111.5</v>
       </c>
       <c r="AC11" t="n">
         <v>11.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2416,7 +2483,7 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
         <v>20</v>
@@ -2440,7 +2507,7 @@
         <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.694</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.44</v>
@@ -2508,25 +2575,25 @@
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T12" t="n">
         <v>43.4</v>
@@ -2535,7 +2602,7 @@
         <v>21.4</v>
       </c>
       <c r="V12" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
         <v>9.800000000000001</v>
@@ -2547,22 +2614,22 @@
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2592,16 +2659,16 @@
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
@@ -2610,31 +2677,31 @@
         <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>-1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
         <v>22</v>
@@ -2756,13 +2823,13 @@
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
@@ -2771,7 +2838,7 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>23</v>
@@ -2783,7 +2850,7 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2801,7 +2868,7 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>6.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>8</v>
@@ -2974,7 +3041,7 @@
         <v>24</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.265</v>
+        <v>0.26</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L15" t="n">
         <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.349</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P15" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T15" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13.3</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,16 +3184,16 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
@@ -3150,13 +3217,13 @@
         <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>7</v>
@@ -3165,16 +3232,16 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA15" t="n">
         <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>20</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>5.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,13 +3366,13 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3341,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3359,10 +3426,10 @@
         <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -3469,16 +3536,16 @@
         <v>-3.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
         <v>29</v>
@@ -3502,7 +3569,7 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
@@ -3538,13 +3605,13 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>29</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" t="n">
         <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>0.549</v>
+        <v>0.54</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3591,10 +3658,10 @@
         <v>38</v>
       </c>
       <c r="J18" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
@@ -3603,19 +3670,19 @@
         <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O18" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P18" t="n">
         <v>20.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S18" t="n">
         <v>31.1</v>
@@ -3624,22 +3691,22 @@
         <v>41.2</v>
       </c>
       <c r="U18" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V18" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="W18" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y18" t="n">
         <v>4.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA18" t="n">
         <v>19.8</v>
@@ -3651,7 +3718,7 @@
         <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3669,13 +3736,13 @@
         <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
         <v>6</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3696,7 +3763,7 @@
         <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-9</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3848,7 +3915,7 @@
         <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="n">
         <v>12</v>
@@ -3872,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
         <v>5</v>
@@ -3887,13 +3954,13 @@
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>7</v>
       </c>
       <c r="AX19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -3940,22 +4007,22 @@
         <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="J20" t="n">
-        <v>83.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K20" t="n">
         <v>0.455</v>
@@ -3970,61 +4037,61 @@
         <v>0.349</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T20" t="n">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
         <v>7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>100</v>
+        <v>100.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4048,49 +4115,49 @@
         <v>16</v>
       </c>
       <c r="AO20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP20" t="n">
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,19 +4204,19 @@
         <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
         <v>7.4</v>
       </c>
       <c r="M21" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O21" t="n">
         <v>13.3</v>
@@ -4158,10 +4225,10 @@
         <v>17.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
         <v>29.2</v>
@@ -4179,13 +4246,13 @@
         <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
         <v>4.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
         <v>18.5</v>
@@ -4194,19 +4261,19 @@
         <v>92.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.6</v>
+        <v>-7.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>29</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH21" t="n">
         <v>19</v>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
@@ -4227,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4248,16 +4315,16 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
         <v>21</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>16</v>
@@ -4391,16 +4458,16 @@
         <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
         <v>17</v>
@@ -4412,7 +4479,7 @@
         <v>27</v>
       </c>
       <c r="AO22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -4421,7 +4488,7 @@
         <v>18</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4439,7 +4506,7 @@
         <v>19</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>12</v>
@@ -4454,7 +4521,7 @@
         <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>0.308</v>
+        <v>0.302</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
         <v>81.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.361</v>
@@ -4522,43 +4589,43 @@
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
         <v>20.6</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA23" t="n">
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4573,16 +4640,16 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
@@ -4600,19 +4667,19 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV23" t="n">
         <v>23</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -4665,67 +4732,67 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.231</v>
+        <v>0.216</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="J24" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K24" t="n">
         <v>0.41</v>
       </c>
       <c r="L24" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M24" t="n">
         <v>24.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.31</v>
+        <v>0.308</v>
       </c>
       <c r="O24" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P24" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="R24" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S24" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U24" t="n">
         <v>20.3</v>
       </c>
       <c r="V24" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="W24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y24" t="n">
         <v>5.5</v>
@@ -4737,13 +4804,13 @@
         <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.8</v>
+        <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,10 +4843,10 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4800,16 +4867,16 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4943,13 +5010,13 @@
         <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM25" t="n">
         <v>5</v>
@@ -4958,7 +5025,7 @@
         <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
@@ -4967,10 +5034,10 @@
         <v>2</v>
       </c>
       <c r="AR25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>19</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E26" t="n">
         <v>34</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.68</v>
       </c>
       <c r="H26" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I26" t="n">
         <v>38.4</v>
       </c>
       <c r="J26" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.444</v>
@@ -5056,58 +5123,58 @@
         <v>10.1</v>
       </c>
       <c r="M26" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O26" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P26" t="n">
         <v>19.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="U26" t="n">
         <v>22.3</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
         <v>102.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5116,10 +5183,10 @@
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
@@ -5143,7 +5210,7 @@
         <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5161,19 +5228,19 @@
         <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA26" t="n">
         <v>24</v>
@@ -5182,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.347</v>
+        <v>0.354</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J27" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O27" t="n">
         <v>23.1</v>
       </c>
       <c r="P27" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="R27" t="n">
         <v>10.9</v>
       </c>
       <c r="S27" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="T27" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V27" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
@@ -5277,46 +5344,46 @@
         <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.6</v>
+        <v>100.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
       </c>
       <c r="AM27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN27" t="n">
         <v>25</v>
@@ -5328,13 +5395,13 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AR27" t="n">
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
@@ -5352,7 +5419,7 @@
         <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
@@ -5364,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F28" t="n">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O28" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
         <v>7.6</v>
@@ -5456,7 +5523,7 @@
         <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
         <v>19.3</v>
@@ -5471,13 +5538,13 @@
         <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
@@ -5489,10 +5556,10 @@
         <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5504,19 +5571,19 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
@@ -5525,7 +5592,7 @@
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
@@ -5534,16 +5601,16 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>4.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG29" t="n">
         <v>6</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5674,7 +5741,7 @@
         <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5692,7 +5759,7 @@
         <v>3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR29" t="n">
         <v>12</v>
@@ -5701,7 +5768,7 @@
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
         <v>19</v>
@@ -5710,7 +5777,7 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -5757,46 +5824,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F30" t="n">
         <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0.353</v>
+        <v>0.34</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J30" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L30" t="n">
         <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O30" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P30" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R30" t="n">
         <v>11.6</v>
@@ -5811,7 +5878,7 @@
         <v>20.2</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W30" t="n">
         <v>6.9</v>
@@ -5823,19 +5890,19 @@
         <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AA30" t="n">
         <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>-2.5</v>
+        <v>-2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
@@ -5844,22 +5911,22 @@
         <v>25</v>
       </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
@@ -5880,34 +5947,34 @@
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW30" t="n">
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA30" t="n">
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" t="n">
         <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0.615</v>
+        <v>0.608</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J31" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L31" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O31" t="n">
         <v>16.2</v>
@@ -5981,16 +6048,16 @@
         <v>0.742</v>
       </c>
       <c r="R31" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S31" t="n">
         <v>33.4</v>
       </c>
       <c r="T31" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U31" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V31" t="n">
         <v>14.8</v>
@@ -6005,22 +6072,22 @@
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA31" t="n">
         <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF31" t="n">
         <v>10</v>
@@ -6029,7 +6096,7 @@
         <v>10</v>
       </c>
       <c r="AH31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6044,7 +6111,7 @@
         <v>26</v>
       </c>
       <c r="AM31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN31" t="n">
         <v>3</v>
@@ -6059,7 +6126,7 @@
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
@@ -6074,7 +6141,7 @@
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
         <v>14</v>
@@ -6083,7 +6150,7 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>17</v>
@@ -6092,7 +6159,7 @@
         <v>17</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-7-2014-15</t>
+          <t>2015-02-07</t>
         </is>
       </c>
     </row>
